--- a/ExcelTest/Merge2.xlsx
+++ b/ExcelTest/Merge2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreasekoyoga/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreasekoyoga/Documents/Net Code/ODCExcelLib/ODCExcelLibraryApp/ExcelTest/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9645BC15-AF41-0A4A-9789-AF549E5DE62D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E424F64-99E2-5148-8483-AED8C09D135A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18360" yWindow="5360" windowWidth="30400" windowHeight="16940" activeTab="2" xr2:uid="{A97C5042-F0E9-0440-BFB1-072601094CB5}"/>
+    <workbookView xWindow="15920" yWindow="5360" windowWidth="30400" windowHeight="16940" activeTab="2" xr2:uid="{A97C5042-F0E9-0440-BFB1-072601094CB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -419,6 +419,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817EA029-6624-EF44-8FC8-3C7BDF15A6FE}">
+  <sheetPr>
+    <tabColor theme="5" tint="-0.249977111117893"/>
+  </sheetPr>
   <dimension ref="A5:A9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -479,6 +482,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B62E063-A667-104D-AD79-2B258367AAD4}">
+  <sheetPr>
+    <tabColor theme="9" tint="-0.249977111117893"/>
+  </sheetPr>
   <dimension ref="AA5:AA8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
